--- a/reports/seo_intel_2026-W20.xlsx
+++ b/reports/seo_intel_2026-W20.xlsx
@@ -462,7 +462,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 11:56 UTC</t>
+          <t>Generated: 2026-05-15 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -475,7 +475,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>2026-04-24</t>
+          <t>2026-05-15</t>
         </is>
       </c>
     </row>
@@ -634,7 +634,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F121"/>
+  <dimension ref="A1:F211"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -711,17 +711,17 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>recording voice recording</t>
+          <t>presents for fathers</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>135000</v>
+        <v>110000</v>
       </c>
       <c r="D3" t="n">
-        <v>118</v>
+        <v>109</v>
       </c>
       <c r="E3" t="n">
-        <v>77</v>
+        <v>15</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -737,17 +737,17 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>presents for fathers</t>
+          <t>book a life</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>110000</v>
+        <v>90500</v>
       </c>
       <c r="D4" t="n">
-        <v>109</v>
+        <v>17</v>
       </c>
       <c r="E4" t="n">
-        <v>15</v>
+        <v>47</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -763,21 +763,21 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>book a life</t>
+          <t>boyfriend questions</t>
         </is>
       </c>
       <c r="C5" t="n">
         <v>90500</v>
       </c>
       <c r="D5" t="n">
-        <v>17</v>
+        <v>43</v>
       </c>
       <c r="E5" t="n">
-        <v>47</v>
+        <v>2</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>https://www.remento.co/</t>
+          <t>https://www.remento.co/journal/questions-to-ask-your-boyfriend</t>
         </is>
       </c>
     </row>
@@ -789,21 +789,21 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>boyfriend questions</t>
+          <t>love questions to ask your boyfriend</t>
         </is>
       </c>
       <c r="C6" t="n">
         <v>90500</v>
       </c>
       <c r="D6" t="n">
-        <v>43</v>
+        <v>12</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-boyfriend</t>
+          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
         </is>
       </c>
     </row>
@@ -815,21 +815,21 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>love questions to ask your boyfriend</t>
+          <t>questions to ask your man</t>
         </is>
       </c>
       <c r="C7" t="n">
         <v>90500</v>
       </c>
       <c r="D7" t="n">
-        <v>12</v>
+        <v>95</v>
       </c>
       <c r="E7" t="n">
-        <v>16</v>
+        <v>2</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
+          <t>https://www.remento.co/journal/questions-to-ask-your-fiance</t>
         </is>
       </c>
     </row>
@@ -841,21 +841,21 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>question boyfriend</t>
+          <t>autobiographical</t>
         </is>
       </c>
       <c r="C8" t="n">
-        <v>90500</v>
+        <v>60500</v>
       </c>
       <c r="D8" t="n">
-        <v>51</v>
+        <v>23</v>
       </c>
       <c r="E8" t="n">
-        <v>0</v>
+        <v>21</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-boyfriend</t>
+          <t>https://www.remento.co/journal/what-is-autobiographical-memory-a-simple-guide</t>
         </is>
       </c>
     </row>
@@ -867,21 +867,21 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>question to ask your boyfriend</t>
+          <t>gift ideas for mom on mother's day</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>90500</v>
+        <v>60500</v>
       </c>
       <c r="D9" t="n">
-        <v>30</v>
+        <v>65</v>
       </c>
       <c r="E9" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
+          <t>https://www.remento.co/journal/mother-day-gift-ideas</t>
         </is>
       </c>
     </row>
@@ -893,21 +893,21 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>questions to ask your man</t>
+          <t>gift suggestions for mother's day</t>
         </is>
       </c>
       <c r="C10" t="n">
-        <v>90500</v>
+        <v>60500</v>
       </c>
       <c r="D10" t="n">
-        <v>95</v>
+        <v>41</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-fiance</t>
+          <t>https://www.remento.co/journal/mother-day-gift-ideas</t>
         </is>
       </c>
     </row>
@@ -919,21 +919,21 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>quiz to ask your boyfriend</t>
+          <t>mothers day idea presents</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>90500</v>
+        <v>60500</v>
       </c>
       <c r="D11" t="n">
-        <v>34</v>
+        <v>79</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>29</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
+          <t>https://www.remento.co/journal/mother-day-gift-ideas</t>
         </is>
       </c>
     </row>
@@ -945,21 +945,21 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>autobiographical</t>
+          <t>questions to ask him</t>
         </is>
       </c>
       <c r="C12" t="n">
         <v>60500</v>
       </c>
       <c r="D12" t="n">
-        <v>23</v>
+        <v>41</v>
       </c>
       <c r="E12" t="n">
-        <v>21</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/what-is-autobiographical-memory-a-simple-guide</t>
+          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
         </is>
       </c>
     </row>
@@ -971,21 +971,21 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>gift ideas for mom on mother's day</t>
+          <t>how do you scan on iphone</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>60500</v>
+        <v>49500</v>
       </c>
       <c r="D13" t="n">
-        <v>65</v>
+        <v>31</v>
       </c>
       <c r="E13" t="n">
         <v>11</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/mother-day-gift-ideas</t>
+          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
         </is>
       </c>
     </row>
@@ -997,21 +997,21 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>gift suggestions for mother's day</t>
+          <t>how to scan iphone</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>60500</v>
+        <v>49500</v>
       </c>
       <c r="D14" t="n">
-        <v>41</v>
+        <v>10</v>
       </c>
       <c r="E14" t="n">
-        <v>29</v>
+        <v>9</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/mother-day-gift-ideas</t>
+          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
         </is>
       </c>
     </row>
@@ -1023,21 +1023,21 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>mothers day idea presents</t>
+          <t>how to scan on iphone</t>
         </is>
       </c>
       <c r="C15" t="n">
-        <v>60500</v>
+        <v>49500</v>
       </c>
       <c r="D15" t="n">
-        <v>79</v>
+        <v>41</v>
       </c>
       <c r="E15" t="n">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/mother-day-gift-ideas</t>
+          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
         </is>
       </c>
     </row>
@@ -1049,21 +1049,21 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>question to ask a lady</t>
+          <t>how to scanner iphone</t>
         </is>
       </c>
       <c r="C16" t="n">
-        <v>60500</v>
+        <v>49500</v>
       </c>
       <c r="D16" t="n">
-        <v>65</v>
+        <v>53</v>
       </c>
       <c r="E16" t="n">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
+          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
         </is>
       </c>
     </row>
@@ -1075,17 +1075,17 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>questions to ask her</t>
+          <t>love questions to ask your gf</t>
         </is>
       </c>
       <c r="C17" t="n">
-        <v>60500</v>
+        <v>49500</v>
       </c>
       <c r="D17" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="E17" t="n">
-        <v>29</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
@@ -1101,21 +1101,21 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>questions to ask him</t>
+          <t>love questions to ask your girlfriend</t>
         </is>
       </c>
       <c r="C18" t="n">
-        <v>60500</v>
+        <v>49500</v>
       </c>
       <c r="D18" t="n">
-        <v>67</v>
+        <v>22</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>15</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
+          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
         </is>
       </c>
     </row>
@@ -1127,21 +1127,21 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>how do you scan on iphone</t>
+          <t>my storyworth</t>
         </is>
       </c>
       <c r="C19" t="n">
         <v>49500</v>
       </c>
       <c r="D19" t="n">
-        <v>31</v>
+        <v>27</v>
       </c>
       <c r="E19" t="n">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
+          <t>https://www.remento.co/journal/storyworth</t>
         </is>
       </c>
     </row>
@@ -1153,21 +1153,21 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>how to scan iphone</t>
+          <t>question ask your girlfriend</t>
         </is>
       </c>
       <c r="C20" t="n">
         <v>49500</v>
       </c>
       <c r="D20" t="n">
-        <v>10</v>
+        <v>17</v>
       </c>
       <c r="E20" t="n">
-        <v>9</v>
+        <v>15</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
+          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
         </is>
       </c>
     </row>
@@ -1179,21 +1179,21 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>how to scan on iphone</t>
+          <t>question to ask a lady</t>
         </is>
       </c>
       <c r="C21" t="n">
         <v>49500</v>
       </c>
       <c r="D21" t="n">
-        <v>41</v>
+        <v>65</v>
       </c>
       <c r="E21" t="n">
-        <v>13</v>
+        <v>29</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
+          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
         </is>
       </c>
     </row>
@@ -1205,21 +1205,21 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>how to scanner iphone</t>
+          <t>question to ask your girlfriend</t>
         </is>
       </c>
       <c r="C22" t="n">
         <v>49500</v>
       </c>
       <c r="D22" t="n">
-        <v>53</v>
+        <v>25</v>
       </c>
       <c r="E22" t="n">
-        <v>12</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
+          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
         </is>
       </c>
     </row>
@@ -1231,21 +1231,21 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>love questions to ask your gf</t>
+          <t>question to ask your girlfriend about love</t>
         </is>
       </c>
       <c r="C23" t="n">
         <v>49500</v>
       </c>
       <c r="D23" t="n">
-        <v>26</v>
+        <v>8</v>
       </c>
       <c r="E23" t="n">
-        <v>5</v>
+        <v>20</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
+          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
         </is>
       </c>
     </row>
@@ -1257,17 +1257,17 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>love questions to ask your girlfriend</t>
+          <t>questions to ask a lady</t>
         </is>
       </c>
       <c r="C24" t="n">
         <v>49500</v>
       </c>
       <c r="D24" t="n">
-        <v>22</v>
+        <v>40</v>
       </c>
       <c r="E24" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
@@ -1283,21 +1283,21 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>my storyworth</t>
+          <t>questions to ask her</t>
         </is>
       </c>
       <c r="C25" t="n">
         <v>49500</v>
       </c>
       <c r="D25" t="n">
-        <v>27</v>
+        <v>34</v>
       </c>
       <c r="E25" t="n">
-        <v>8</v>
+        <v>29</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/storyworth</t>
+          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
         </is>
       </c>
     </row>
@@ -1309,17 +1309,17 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>question ask your girlfriend</t>
+          <t>questions to ask your gf</t>
         </is>
       </c>
       <c r="C26" t="n">
         <v>49500</v>
       </c>
       <c r="D26" t="n">
-        <v>17</v>
+        <v>47</v>
       </c>
       <c r="E26" t="n">
-        <v>15</v>
+        <v>2</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
@@ -1335,17 +1335,17 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>question to ask your girlfriend</t>
+          <t>questions to ask your gf about love</t>
         </is>
       </c>
       <c r="C27" t="n">
         <v>49500</v>
       </c>
       <c r="D27" t="n">
-        <v>25</v>
+        <v>30</v>
       </c>
       <c r="E27" t="n">
-        <v>5</v>
+        <v>13</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
@@ -1361,7 +1361,7 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>question to ask your girlfriend about love</t>
+          <t>storyworth</t>
         </is>
       </c>
       <c r="C28" t="n">
@@ -1371,11 +1371,11 @@
         <v>8</v>
       </c>
       <c r="E28" t="n">
-        <v>20</v>
+        <v>46</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/36-questions-to-fall-in-love-or-at-least-bring-you-closer-together</t>
+          <t>https://www.remento.co/journal/storyworth</t>
         </is>
       </c>
     </row>
@@ -1387,21 +1387,21 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>questions to ask a girlfriend</t>
+          <t>babybook</t>
         </is>
       </c>
       <c r="C29" t="n">
-        <v>49500</v>
+        <v>40500</v>
       </c>
       <c r="D29" t="n">
-        <v>15</v>
+        <v>43</v>
       </c>
       <c r="E29" t="n">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
+          <t>https://www.remento.co/landing/babybook</t>
         </is>
       </c>
     </row>
@@ -1413,21 +1413,21 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>questions to ask a lady</t>
+          <t>how to scan a document with an iphone</t>
         </is>
       </c>
       <c r="C30" t="n">
-        <v>49500</v>
+        <v>40500</v>
       </c>
       <c r="D30" t="n">
-        <v>40</v>
+        <v>76</v>
       </c>
       <c r="E30" t="n">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
+          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
         </is>
       </c>
     </row>
@@ -1439,21 +1439,21 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>questions to ask your gf</t>
+          <t>how to scan a document with iphone</t>
         </is>
       </c>
       <c r="C31" t="n">
-        <v>49500</v>
+        <v>40500</v>
       </c>
       <c r="D31" t="n">
-        <v>47</v>
+        <v>40</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>16</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>https://www.remento.co/journal/questions-to-ask-your-girlfriend</t>
+          <t>https://www.remento.co/journal/the-hidden-your-photo-scanner-on-your-iphone-and-ipad-heres-how-to-use-it</t>
         </is>
       </c>
     </row>
@@ -1465,21 +1465,21 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>questions to ask your gf</t>
+          <t>gift ia</t>
         </is>
       </c>
       <c r="C32" t="n">
-        <v>49500</v>
+        <v>60500</v>
       </c>
       <c r="D32" t="n">
-        <v>50</v>
+        <v>90</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>49</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/150-questions-to-ask-your-girlfriend-about-your-relationship/</t>
+          <t>https://meminto.com/meminto-ai-tools/free-ai-gift-ideas-generator/</t>
         </is>
       </c>
     </row>
@@ -1491,17 +1491,17 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>questions to ask your girlfriend</t>
+          <t>questions ask girlfriend</t>
         </is>
       </c>
       <c r="C33" t="n">
         <v>49500</v>
       </c>
       <c r="D33" t="n">
-        <v>67</v>
+        <v>81</v>
       </c>
       <c r="E33" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
@@ -1517,21 +1517,21 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>remento</t>
+          <t>questions to ask your gf</t>
         </is>
       </c>
       <c r="C34" t="n">
-        <v>18100</v>
+        <v>49500</v>
       </c>
       <c r="D34" t="n">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="E34" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>https://meminto.com/remento-vs-meminto-best-remento-alternative/</t>
+          <t>https://meminto.com/blog/150-questions-to-ask-your-girlfriend-about-your-relationship/</t>
         </is>
       </c>
     </row>
@@ -1543,21 +1543,21 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>grandparent gift ideas</t>
+          <t>questions to ask your girlfriend</t>
         </is>
       </c>
       <c r="C35" t="n">
-        <v>14800</v>
+        <v>49500</v>
       </c>
       <c r="D35" t="n">
-        <v>99</v>
+        <v>67</v>
       </c>
       <c r="E35" t="n">
         <v>0</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/20-thoughtful-gifts-for-new-grandparents/</t>
+          <t>https://meminto.com/blog/150-questions-to-ask-your-girlfriend-about-your-relationship/</t>
         </is>
       </c>
     </row>
@@ -1569,21 +1569,21 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>grandparents gift idea</t>
+          <t>remento</t>
         </is>
       </c>
       <c r="C36" t="n">
-        <v>14800</v>
+        <v>18100</v>
       </c>
       <c r="D36" t="n">
-        <v>46</v>
+        <v>40</v>
       </c>
       <c r="E36" t="n">
-        <v>0</v>
+        <v>9</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/20-thoughtful-gifts-for-new-grandparents/</t>
+          <t>https://meminto.com/remento-vs-meminto-best-remento-alternative/</t>
         </is>
       </c>
     </row>
@@ -1595,14 +1595,14 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>presents grandparents</t>
+          <t>grandparents gift idea</t>
         </is>
       </c>
       <c r="C37" t="n">
         <v>14800</v>
       </c>
       <c r="D37" t="n">
-        <v>57</v>
+        <v>46</v>
       </c>
       <c r="E37" t="n">
         <v>0</v>
@@ -1621,21 +1621,21 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>gift ideas for 50th wedding anniversary</t>
+          <t>presents grandparents</t>
         </is>
       </c>
       <c r="C38" t="n">
-        <v>12100</v>
+        <v>14800</v>
       </c>
       <c r="D38" t="n">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="E38" t="n">
         <v>0</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/the-most-personal-50th-wedding-anniversary-gift-ideas/</t>
+          <t>https://meminto.com/blog/20-thoughtful-gifts-for-new-grandparents/</t>
         </is>
       </c>
     </row>
@@ -1647,17 +1647,17 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>wedding anniversary gifts 50th</t>
+          <t>gift ideas for 50th wedding anniversary</t>
         </is>
       </c>
       <c r="C39" t="n">
         <v>12100</v>
       </c>
       <c r="D39" t="n">
-        <v>73</v>
+        <v>55</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
@@ -1673,21 +1673,21 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>gifts for a couples</t>
+          <t>wedding anniversary gifts 50th</t>
         </is>
       </c>
       <c r="C40" t="n">
-        <v>9900</v>
+        <v>12100</v>
       </c>
       <c r="D40" t="n">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="E40" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/30-gift-ideas-for-couples-who-have-everything/</t>
+          <t>https://meminto.com/blog/the-most-personal-50th-wedding-anniversary-gift-ideas/</t>
         </is>
       </c>
     </row>
@@ -1699,7 +1699,7 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>ideal gift for a girlfriend</t>
+          <t>gifts for a couples</t>
         </is>
       </c>
       <c r="C41" t="n">
@@ -1709,11 +1709,11 @@
         <v>75</v>
       </c>
       <c r="E41" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/gifts-ideas-for-girlfriend-or-wife/</t>
+          <t>https://meminto.com/blog/30-gift-ideas-for-couples-who-have-everything/</t>
         </is>
       </c>
     </row>
@@ -1725,14 +1725,14 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>present suggestions for girlfriend</t>
+          <t>ideal gift for a girlfriend</t>
         </is>
       </c>
       <c r="C42" t="n">
         <v>9900</v>
       </c>
       <c r="D42" t="n">
-        <v>58</v>
+        <v>75</v>
       </c>
       <c r="E42" t="n">
         <v>4</v>
@@ -1751,21 +1751,21 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>tradition in family</t>
+          <t>present suggestions for girlfriend</t>
         </is>
       </c>
       <c r="C43" t="n">
         <v>9900</v>
       </c>
       <c r="D43" t="n">
-        <v>74</v>
+        <v>58</v>
       </c>
       <c r="E43" t="n">
-        <v>21</v>
+        <v>4</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/50-family-tradition-examples-for-family-reunion/</t>
+          <t>https://meminto.com/blog/gifts-ideas-for-girlfriend-or-wife/</t>
         </is>
       </c>
     </row>
@@ -1777,21 +1777,21 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>family loving quotes</t>
+          <t>tradition in family</t>
         </is>
       </c>
       <c r="C44" t="n">
-        <v>8100</v>
+        <v>9900</v>
       </c>
       <c r="D44" t="n">
-        <v>29</v>
+        <v>74</v>
       </c>
       <c r="E44" t="n">
-        <v>11</v>
+        <v>21</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/100-making-memories-with-family-quotes-captions-for-instagram/</t>
+          <t>https://meminto.com/blog/50-family-tradition-examples-for-family-reunion/</t>
         </is>
       </c>
     </row>
@@ -1803,21 +1803,21 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>memories books</t>
+          <t>family loving quotes</t>
         </is>
       </c>
       <c r="C45" t="n">
         <v>8100</v>
       </c>
       <c r="D45" t="n">
-        <v>90</v>
+        <v>29</v>
       </c>
       <c r="E45" t="n">
-        <v>0</v>
+        <v>11</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/how-to-create-a-memory-book-online/</t>
+          <t>https://meminto.com/blog/100-making-memories-with-family-quotes-captions-for-instagram/</t>
         </is>
       </c>
     </row>
@@ -1829,21 +1829,21 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>best gift ideas for grandparents</t>
+          <t>memories books</t>
         </is>
       </c>
       <c r="C46" t="n">
-        <v>6600</v>
+        <v>8100</v>
       </c>
       <c r="D46" t="n">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="E46" t="n">
         <v>0</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/20-thoughtful-gifts-for-new-grandparents/</t>
+          <t>https://meminto.com/blog/how-to-create-a-memory-book-online/</t>
         </is>
       </c>
     </row>
@@ -1855,14 +1855,14 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>best gift to grandparents</t>
+          <t>best gift ideas for grandparents</t>
         </is>
       </c>
       <c r="C47" t="n">
         <v>6600</v>
       </c>
       <c r="D47" t="n">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="E47" t="n">
         <v>0</v>
@@ -1881,14 +1881,14 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>best gifts grandparents</t>
+          <t>best gift to grandparents</t>
         </is>
       </c>
       <c r="C48" t="n">
         <v>6600</v>
       </c>
       <c r="D48" t="n">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="E48" t="n">
         <v>0</v>
@@ -1907,14 +1907,14 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>best presents grandparents</t>
+          <t>best gifts grandparents</t>
         </is>
       </c>
       <c r="C49" t="n">
         <v>6600</v>
       </c>
       <c r="D49" t="n">
-        <v>93</v>
+        <v>78</v>
       </c>
       <c r="E49" t="n">
         <v>0</v>
@@ -1933,14 +1933,14 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>christmas gift ideas for grandparents</t>
+          <t>best presents grandparents</t>
         </is>
       </c>
       <c r="C50" t="n">
         <v>6600</v>
       </c>
       <c r="D50" t="n">
-        <v>95</v>
+        <v>93</v>
       </c>
       <c r="E50" t="n">
         <v>0</v>
@@ -1959,14 +1959,14 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>christmas gifts for grandparent</t>
+          <t>christmas gift ideas for grandparents</t>
         </is>
       </c>
       <c r="C51" t="n">
         <v>6600</v>
       </c>
       <c r="D51" t="n">
-        <v>72</v>
+        <v>95</v>
       </c>
       <c r="E51" t="n">
         <v>0</v>
@@ -1985,14 +1985,14 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>christmas gifts for grandparents</t>
+          <t>christmas gifts for grandparent</t>
         </is>
       </c>
       <c r="C52" t="n">
         <v>6600</v>
       </c>
       <c r="D52" t="n">
-        <v>52</v>
+        <v>72</v>
       </c>
       <c r="E52" t="n">
         <v>0</v>
@@ -2011,14 +2011,14 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>christmas gifts to give grandparents</t>
+          <t>christmas gifts for grandparents</t>
         </is>
       </c>
       <c r="C53" t="n">
         <v>6600</v>
       </c>
       <c r="D53" t="n">
-        <v>36</v>
+        <v>52</v>
       </c>
       <c r="E53" t="n">
         <v>0</v>
@@ -2037,17 +2037,17 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>christmas present for grandparents</t>
+          <t>christmas gifts to give grandparents</t>
         </is>
       </c>
       <c r="C54" t="n">
         <v>6600</v>
       </c>
       <c r="D54" t="n">
-        <v>72</v>
+        <v>36</v>
       </c>
       <c r="E54" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
@@ -2063,17 +2063,17 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>christmas present ideas grandparents</t>
+          <t>christmas present for grandparents</t>
         </is>
       </c>
       <c r="C55" t="n">
         <v>6600</v>
       </c>
       <c r="D55" t="n">
-        <v>80</v>
+        <v>72</v>
       </c>
       <c r="E55" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F55" t="inlineStr">
         <is>
@@ -2089,17 +2089,17 @@
       </c>
       <c r="B56" t="inlineStr">
         <is>
-          <t>christmas presents for grandparents</t>
+          <t>christmas present ideas grandparents</t>
         </is>
       </c>
       <c r="C56" t="n">
         <v>6600</v>
       </c>
       <c r="D56" t="n">
-        <v>55</v>
+        <v>80</v>
       </c>
       <c r="E56" t="n">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
@@ -2115,17 +2115,17 @@
       </c>
       <c r="B57" t="inlineStr">
         <is>
-          <t>christmas presents ideas for grandparents</t>
+          <t>christmas presents for grandparents</t>
         </is>
       </c>
       <c r="C57" t="n">
         <v>6600</v>
       </c>
       <c r="D57" t="n">
-        <v>80</v>
+        <v>55</v>
       </c>
       <c r="E57" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
@@ -2141,14 +2141,14 @@
       </c>
       <c r="B58" t="inlineStr">
         <is>
-          <t>gift for grandparents christmas</t>
+          <t>christmas presents ideas for grandparents</t>
         </is>
       </c>
       <c r="C58" t="n">
         <v>6600</v>
       </c>
       <c r="D58" t="n">
-        <v>63</v>
+        <v>80</v>
       </c>
       <c r="E58" t="n">
         <v>0</v>
@@ -2167,21 +2167,21 @@
       </c>
       <c r="B59" t="inlineStr">
         <is>
-          <t>gift ideas for a girlfriend</t>
+          <t>gift for grandparents christmas</t>
         </is>
       </c>
       <c r="C59" t="n">
         <v>6600</v>
       </c>
       <c r="D59" t="n">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="E59" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/gifts-ideas-for-girlfriend-or-wife/</t>
+          <t>https://meminto.com/blog/20-thoughtful-gifts-for-new-grandparents/</t>
         </is>
       </c>
     </row>
@@ -2193,17 +2193,17 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>gift ideas for the girlfriend</t>
+          <t>gift ideas for a girlfriend</t>
         </is>
       </c>
       <c r="C60" t="n">
         <v>6600</v>
       </c>
       <c r="D60" t="n">
-        <v>62</v>
+        <v>66</v>
       </c>
       <c r="E60" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
@@ -2219,21 +2219,21 @@
       </c>
       <c r="B61" t="inlineStr">
         <is>
-          <t>gifts to give grandparents for christmas</t>
+          <t>gift ideas for the girlfriend</t>
         </is>
       </c>
       <c r="C61" t="n">
         <v>6600</v>
       </c>
       <c r="D61" t="n">
-        <v>70</v>
+        <v>62</v>
       </c>
       <c r="E61" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>https://meminto.com/blog/20-thoughtful-gifts-for-new-grandparents/</t>
+          <t>https://meminto.com/blog/gifts-ideas-for-girlfriend-or-wife/</t>
         </is>
       </c>
     </row>
@@ -2661,21 +2661,21 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>what day mother's day</t>
+          <t>christmas gifts for mother</t>
         </is>
       </c>
       <c r="C78" t="n">
-        <v>60500</v>
+        <v>49500</v>
       </c>
       <c r="D78" t="n">
-        <v>7</v>
+        <v>84</v>
       </c>
       <c r="E78" t="n">
-        <v>41</v>
+        <v>4</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>https://welcome.storyworth.com/blog/when-is-mothers-day-complete-guide</t>
+          <t>https://welcome.storyworth.com/</t>
         </is>
       </c>
     </row>
@@ -2687,21 +2687,21 @@
       </c>
       <c r="B79" t="inlineStr">
         <is>
-          <t>christmas gifts for mother</t>
+          <t>my storyworth</t>
         </is>
       </c>
       <c r="C79" t="n">
         <v>49500</v>
       </c>
       <c r="D79" t="n">
-        <v>84</v>
+        <v>1</v>
       </c>
       <c r="E79" t="n">
-        <v>4</v>
+        <v>8</v>
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>https://welcome.storyworth.com/</t>
+          <t>https://www.storyworth.com/hello-again</t>
         </is>
       </c>
     </row>
@@ -2713,7 +2713,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>my storyworth</t>
+          <t>storyworth</t>
         </is>
       </c>
       <c r="C80" t="n">
@@ -2723,11 +2723,11 @@
         <v>1</v>
       </c>
       <c r="E80" t="n">
-        <v>8</v>
+        <v>46</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>https://www.storyworth.com/hello-again</t>
+          <t>https://welcome.storyworth.com/</t>
         </is>
       </c>
     </row>
@@ -2739,17 +2739,17 @@
       </c>
       <c r="B81" t="inlineStr">
         <is>
-          <t>storyworth</t>
+          <t>xmas gifts for mothers</t>
         </is>
       </c>
       <c r="C81" t="n">
         <v>49500</v>
       </c>
       <c r="D81" t="n">
-        <v>1</v>
+        <v>106</v>
       </c>
       <c r="E81" t="n">
-        <v>46</v>
+        <v>4</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
@@ -2765,17 +2765,17 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>xmas gifts for mothers</t>
+          <t>christmas present for dad</t>
         </is>
       </c>
       <c r="C82" t="n">
-        <v>49500</v>
+        <v>33100</v>
       </c>
       <c r="D82" t="n">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="E82" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="F82" t="inlineStr">
         <is>
@@ -2791,17 +2791,17 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>christmas present for dad</t>
+          <t>christmas present for father</t>
         </is>
       </c>
       <c r="C83" t="n">
         <v>33100</v>
       </c>
       <c r="D83" t="n">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="E83" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="F83" t="inlineStr">
         <is>
@@ -2817,17 +2817,17 @@
       </c>
       <c r="B84" t="inlineStr">
         <is>
-          <t>christmas present for father</t>
+          <t>christmas presents for your dad</t>
         </is>
       </c>
       <c r="C84" t="n">
         <v>33100</v>
       </c>
       <c r="D84" t="n">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="E84" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F84" t="inlineStr">
         <is>
@@ -2843,17 +2843,17 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>christmas presents for your dad</t>
+          <t>dad xmas presents</t>
         </is>
       </c>
       <c r="C85" t="n">
         <v>33100</v>
       </c>
       <c r="D85" t="n">
-        <v>88</v>
+        <v>110</v>
       </c>
       <c r="E85" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F85" t="inlineStr">
         <is>
@@ -2869,17 +2869,17 @@
       </c>
       <c r="B86" t="inlineStr">
         <is>
-          <t>dad xmas presents</t>
+          <t>father birthday gifts</t>
         </is>
       </c>
       <c r="C86" t="n">
         <v>33100</v>
       </c>
       <c r="D86" t="n">
-        <v>102</v>
+        <v>74</v>
       </c>
       <c r="E86" t="n">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="F86" t="inlineStr">
         <is>
@@ -2895,14 +2895,14 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>father birthday gifts</t>
+          <t>fathers christmas presents</t>
         </is>
       </c>
       <c r="C87" t="n">
         <v>33100</v>
       </c>
       <c r="D87" t="n">
-        <v>74</v>
+        <v>68</v>
       </c>
       <c r="E87" t="n">
         <v>9</v>
@@ -2921,14 +2921,14 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>fathers christmas presents</t>
+          <t>get to know you questions</t>
         </is>
       </c>
       <c r="C88" t="n">
         <v>33100</v>
       </c>
       <c r="D88" t="n">
-        <v>68</v>
+        <v>47</v>
       </c>
       <c r="E88" t="n">
         <v>9</v>
@@ -2947,17 +2947,17 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>get to know you questions</t>
+          <t>gifts for dad this christmas</t>
         </is>
       </c>
       <c r="C89" t="n">
         <v>33100</v>
       </c>
       <c r="D89" t="n">
-        <v>47</v>
+        <v>56</v>
       </c>
       <c r="E89" t="n">
-        <v>9</v>
+        <v>6</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
@@ -2973,17 +2973,17 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>gifts for dad this christmas</t>
+          <t>gifts for dads birthday</t>
         </is>
       </c>
       <c r="C90" t="n">
         <v>33100</v>
       </c>
       <c r="D90" t="n">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="E90" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
@@ -2999,17 +2999,17 @@
       </c>
       <c r="B91" t="inlineStr">
         <is>
-          <t>gifts for dads birthday</t>
+          <t>xmas gift for father</t>
         </is>
       </c>
       <c r="C91" t="n">
         <v>33100</v>
       </c>
       <c r="D91" t="n">
-        <v>80</v>
+        <v>34</v>
       </c>
       <c r="E91" t="n">
-        <v>7</v>
+        <v>11</v>
       </c>
       <c r="F91" t="inlineStr">
         <is>
@@ -3129,21 +3129,21 @@
       </c>
       <c r="B96" t="inlineStr">
         <is>
-          <t>book as gift</t>
+          <t>book of stories</t>
         </is>
       </c>
       <c r="C96" t="n">
-        <v>4400</v>
+        <v>5400</v>
       </c>
       <c r="D96" t="n">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="E96" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/a-memory-book-is-the-ideal-gift-for-someone-whose-life-you-wish-to-celebrate-read-about-the-process-and-get-inspiration-for-a-personal-gift-here/</t>
+          <t>https://storykeeper.com/</t>
         </is>
       </c>
     </row>
@@ -3155,21 +3155,21 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>saving stories</t>
+          <t>book as gift</t>
         </is>
       </c>
       <c r="C97" t="n">
         <v>4400</v>
       </c>
       <c r="D97" t="n">
-        <v>9</v>
+        <v>36</v>
       </c>
       <c r="E97" t="n">
-        <v>36</v>
+        <v>4</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/</t>
+          <t>https://storykeeper.com/a-memory-book-is-the-ideal-gift-for-someone-whose-life-you-wish-to-celebrate-read-about-the-process-and-get-inspiration-for-a-personal-gift-here/</t>
         </is>
       </c>
     </row>
@@ -3181,21 +3181,21 @@
       </c>
       <c r="B98" t="inlineStr">
         <is>
-          <t>difference between a memoir and an autobiography</t>
+          <t>saving stories</t>
         </is>
       </c>
       <c r="C98" t="n">
-        <v>1900</v>
+        <v>4400</v>
       </c>
       <c r="D98" t="n">
-        <v>108</v>
+        <v>9</v>
       </c>
       <c r="E98" t="n">
-        <v>0</v>
+        <v>36</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/blog/memoir-vs-autobiography-capturing-your-legacy-with-interview-questions-for-parents/</t>
+          <t>https://storykeeper.com/</t>
         </is>
       </c>
     </row>
@@ -3207,21 +3207,21 @@
       </c>
       <c r="B99" t="inlineStr">
         <is>
-          <t>my life in a book</t>
+          <t>difference between a memoir and an autobiography</t>
         </is>
       </c>
       <c r="C99" t="n">
         <v>1900</v>
       </c>
       <c r="D99" t="n">
-        <v>20</v>
+        <v>108</v>
       </c>
       <c r="E99" t="n">
-        <v>6</v>
+        <v>0</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/storykeeper-vs-mylifeinabook/</t>
+          <t>https://storykeeper.com/blog/memoir-vs-autobiography-capturing-your-legacy-with-interview-questions-for-parents/</t>
         </is>
       </c>
     </row>
@@ -3233,21 +3233,21 @@
       </c>
       <c r="B100" t="inlineStr">
         <is>
-          <t>story keeper</t>
+          <t>my life in a book</t>
         </is>
       </c>
       <c r="C100" t="n">
         <v>1900</v>
       </c>
       <c r="D100" t="n">
-        <v>1</v>
+        <v>20</v>
       </c>
       <c r="E100" t="n">
-        <v>2</v>
+        <v>6</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/</t>
+          <t>https://storykeeper.com/storykeeper-vs-mylifeinabook/</t>
         </is>
       </c>
     </row>
@@ -3259,21 +3259,21 @@
       </c>
       <c r="B101" t="inlineStr">
         <is>
-          <t>storykeepers</t>
+          <t>remento reviews</t>
         </is>
       </c>
       <c r="C101" t="n">
         <v>1900</v>
       </c>
       <c r="D101" t="n">
-        <v>32</v>
+        <v>47</v>
       </c>
       <c r="E101" t="n">
         <v>0</v>
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/</t>
+          <t>https://storykeeper.com/storykeeper-vs-remento-a-comparison-of-two-life-story-book-services/</t>
         </is>
       </c>
     </row>
@@ -3285,17 +3285,17 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>story keeper book</t>
+          <t>story keeper</t>
         </is>
       </c>
       <c r="C102" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="D102" t="n">
-        <v>7</v>
+        <v>1</v>
       </c>
       <c r="E102" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="F102" t="inlineStr">
         <is>
@@ -3311,17 +3311,17 @@
       </c>
       <c r="B103" t="inlineStr">
         <is>
-          <t>storykeeper book</t>
+          <t>storykeepers</t>
         </is>
       </c>
       <c r="C103" t="n">
-        <v>1600</v>
+        <v>1900</v>
       </c>
       <c r="D103" t="n">
-        <v>2</v>
+        <v>32</v>
       </c>
       <c r="E103" t="n">
-        <v>12</v>
+        <v>0</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
@@ -3337,14 +3337,14 @@
       </c>
       <c r="B104" t="inlineStr">
         <is>
-          <t>the story keeper</t>
+          <t>story keeper book</t>
         </is>
       </c>
       <c r="C104" t="n">
         <v>1600</v>
       </c>
       <c r="D104" t="n">
-        <v>18</v>
+        <v>7</v>
       </c>
       <c r="E104" t="n">
         <v>0</v>
@@ -3363,17 +3363,17 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>the storykeeper</t>
+          <t>storykeeper book</t>
         </is>
       </c>
       <c r="C105" t="n">
         <v>1600</v>
       </c>
       <c r="D105" t="n">
-        <v>6</v>
+        <v>2</v>
       </c>
       <c r="E105" t="n">
-        <v>0</v>
+        <v>12</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
@@ -3389,21 +3389,21 @@
       </c>
       <c r="B106" t="inlineStr">
         <is>
-          <t>remento book</t>
+          <t>the story keeper</t>
         </is>
       </c>
       <c r="C106" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="D106" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E106" t="n">
-        <v>8</v>
+        <v>0</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/ie/storykeeper-vs-remento-a-comparison-of-two-life-story-book-services/</t>
+          <t>https://storykeeper.com/</t>
         </is>
       </c>
     </row>
@@ -3415,17 +3415,17 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>stories planner</t>
+          <t>the storykeeper</t>
         </is>
       </c>
       <c r="C107" t="n">
-        <v>1000</v>
+        <v>1600</v>
       </c>
       <c r="D107" t="n">
-        <v>69</v>
+        <v>6</v>
       </c>
       <c r="E107" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
@@ -3441,21 +3441,21 @@
       </c>
       <c r="B108" t="inlineStr">
         <is>
-          <t>memory keeper</t>
+          <t>remento book</t>
         </is>
       </c>
       <c r="C108" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="D108" t="n">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="E108" t="n">
-        <v>2</v>
+        <v>8</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/</t>
+          <t>https://storykeeper.com/ie/storykeeper-vs-remento-a-comparison-of-two-life-story-book-services/</t>
         </is>
       </c>
     </row>
@@ -3467,17 +3467,17 @@
       </c>
       <c r="B109" t="inlineStr">
         <is>
-          <t>parent memory book</t>
+          <t>stories planner</t>
         </is>
       </c>
       <c r="C109" t="n">
-        <v>880</v>
+        <v>1000</v>
       </c>
       <c r="D109" t="n">
-        <v>6</v>
+        <v>69</v>
       </c>
       <c r="E109" t="n">
-        <v>8</v>
+        <v>1</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
@@ -3493,17 +3493,17 @@
       </c>
       <c r="B110" t="inlineStr">
         <is>
-          <t>parents memory book</t>
+          <t>memory keeper</t>
         </is>
       </c>
       <c r="C110" t="n">
         <v>880</v>
       </c>
       <c r="D110" t="n">
-        <v>6</v>
+        <v>31</v>
       </c>
       <c r="E110" t="n">
-        <v>10</v>
+        <v>2</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
@@ -3519,21 +3519,21 @@
       </c>
       <c r="B111" t="inlineStr">
         <is>
-          <t>what is the difference between a memoir and an autobiography</t>
+          <t>parent memory book</t>
         </is>
       </c>
       <c r="C111" t="n">
         <v>880</v>
       </c>
       <c r="D111" t="n">
-        <v>110</v>
+        <v>6</v>
       </c>
       <c r="E111" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/blog/memoir-vs-autobiography-capturing-your-legacy-with-interview-questions-for-parents/</t>
+          <t>https://storykeeper.com/</t>
         </is>
       </c>
     </row>
@@ -3545,17 +3545,17 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>grandparents memory book</t>
+          <t>parents memory book</t>
         </is>
       </c>
       <c r="C112" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="D112" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="E112" t="n">
-        <v>4</v>
+        <v>10</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
@@ -3571,21 +3571,21 @@
       </c>
       <c r="B113" t="inlineStr">
         <is>
-          <t>memories book for grandparents</t>
+          <t>what is the difference between a memoir and an autobiography</t>
         </is>
       </c>
       <c r="C113" t="n">
-        <v>720</v>
+        <v>880</v>
       </c>
       <c r="D113" t="n">
-        <v>43</v>
+        <v>110</v>
       </c>
       <c r="E113" t="n">
         <v>0</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/</t>
+          <t>https://storykeeper.com/blog/memoir-vs-autobiography-capturing-your-legacy-with-interview-questions-for-parents/</t>
         </is>
       </c>
     </row>
@@ -3597,17 +3597,17 @@
       </c>
       <c r="B114" t="inlineStr">
         <is>
-          <t>memory book for grandparents</t>
+          <t>grandparents memory book</t>
         </is>
       </c>
       <c r="C114" t="n">
         <v>720</v>
       </c>
       <c r="D114" t="n">
-        <v>11</v>
+        <v>7</v>
       </c>
       <c r="E114" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
@@ -3623,17 +3623,17 @@
       </c>
       <c r="B115" t="inlineStr">
         <is>
-          <t>memory book grandparents</t>
+          <t>memories book for grandparents</t>
         </is>
       </c>
       <c r="C115" t="n">
         <v>720</v>
       </c>
       <c r="D115" t="n">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="E115" t="n">
-        <v>5</v>
+        <v>0</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
@@ -3649,17 +3649,17 @@
       </c>
       <c r="B116" t="inlineStr">
         <is>
-          <t>personalised book for grandma</t>
+          <t>memory book for grandparents</t>
         </is>
       </c>
       <c r="C116" t="n">
         <v>720</v>
       </c>
       <c r="D116" t="n">
-        <v>35</v>
+        <v>11</v>
       </c>
       <c r="E116" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
@@ -3675,17 +3675,17 @@
       </c>
       <c r="B117" t="inlineStr">
         <is>
-          <t>personalised books for grandparents</t>
+          <t>memory book grandparents</t>
         </is>
       </c>
       <c r="C117" t="n">
         <v>720</v>
       </c>
       <c r="D117" t="n">
-        <v>31</v>
+        <v>9</v>
       </c>
       <c r="E117" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
@@ -3701,21 +3701,21 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>personalized book for grandpa</t>
+          <t>personalised book for grandma</t>
         </is>
       </c>
       <c r="C118" t="n">
         <v>720</v>
       </c>
       <c r="D118" t="n">
-        <v>66</v>
+        <v>35</v>
       </c>
       <c r="E118" t="n">
         <v>0</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/blog/more-than-just-a-gift-why-and-how-to-create-a-life-story-book-for-grandparents/</t>
+          <t>https://storykeeper.com/</t>
         </is>
       </c>
     </row>
@@ -3727,14 +3727,14 @@
       </c>
       <c r="B119" t="inlineStr">
         <is>
-          <t>personalized book for grandparents</t>
+          <t>personalised books for grandparents</t>
         </is>
       </c>
       <c r="C119" t="n">
         <v>720</v>
       </c>
       <c r="D119" t="n">
-        <v>67</v>
+        <v>31</v>
       </c>
       <c r="E119" t="n">
         <v>0</v>
@@ -3753,21 +3753,21 @@
       </c>
       <c r="B120" t="inlineStr">
         <is>
-          <t>personalized book from grandparents</t>
+          <t>personalized book for grandpa</t>
         </is>
       </c>
       <c r="C120" t="n">
         <v>720</v>
       </c>
       <c r="D120" t="n">
-        <v>42</v>
+        <v>66</v>
       </c>
       <c r="E120" t="n">
         <v>0</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>https://storykeeper.com/</t>
+          <t>https://storykeeper.com/blog/more-than-just-a-gift-why-and-how-to-create-a-life-story-book-for-grandparents/</t>
         </is>
       </c>
     </row>
@@ -3779,14 +3779,14 @@
       </c>
       <c r="B121" t="inlineStr">
         <is>
-          <t>personalized books for grandma</t>
+          <t>personalized book for grandparents</t>
         </is>
       </c>
       <c r="C121" t="n">
         <v>720</v>
       </c>
       <c r="D121" t="n">
-        <v>43</v>
+        <v>67</v>
       </c>
       <c r="E121" t="n">
         <v>0</v>
@@ -3794,6 +3794,2346 @@
       <c r="F121" t="inlineStr">
         <is>
           <t>https://storykeeper.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B122" t="inlineStr">
+        <is>
+          <t>artificial intelligence companion</t>
+        </is>
+      </c>
+      <c r="C122" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D122" t="n">
+        <v>56</v>
+      </c>
+      <c r="E122" t="n">
+        <v>43</v>
+      </c>
+      <c r="F122" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>exercise and the elderly</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D123" t="n">
+        <v>85</v>
+      </c>
+      <c r="E123" t="n">
+        <v>35</v>
+      </c>
+      <c r="F123" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/exercise-for-elderly-staying-active-at-any-age</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>exercise in elderly</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D124" t="n">
+        <v>52</v>
+      </c>
+      <c r="E124" t="n">
+        <v>69</v>
+      </c>
+      <c r="F124" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/exercise-for-elderly-staying-active-at-any-age</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B125" t="inlineStr">
+        <is>
+          <t>companion robot</t>
+        </is>
+      </c>
+      <c r="C125" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D125" t="n">
+        <v>10</v>
+      </c>
+      <c r="E125" t="n">
+        <v>8</v>
+      </c>
+      <c r="F125" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B126" t="inlineStr">
+        <is>
+          <t>companion robots</t>
+        </is>
+      </c>
+      <c r="C126" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D126" t="n">
+        <v>10</v>
+      </c>
+      <c r="E126" t="n">
+        <v>20</v>
+      </c>
+      <c r="F126" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B127" t="inlineStr">
+        <is>
+          <t>robot companion</t>
+        </is>
+      </c>
+      <c r="C127" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D127" t="n">
+        <v>9</v>
+      </c>
+      <c r="E127" t="n">
+        <v>13</v>
+      </c>
+      <c r="F127" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>robotic companionship</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D128" t="n">
+        <v>8</v>
+      </c>
+      <c r="E128" t="n">
+        <v>13</v>
+      </c>
+      <c r="F128" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>elliq</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D129" t="n">
+        <v>1</v>
+      </c>
+      <c r="E129" t="n">
+        <v>14</v>
+      </c>
+      <c r="F129" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>el q</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>2400</v>
+      </c>
+      <c r="D130" t="n">
+        <v>7</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0</v>
+      </c>
+      <c r="F130" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B131" t="inlineStr">
+        <is>
+          <t>ai companion robot</t>
+        </is>
+      </c>
+      <c r="C131" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D131" t="n">
+        <v>8</v>
+      </c>
+      <c r="E131" t="n">
+        <v>20</v>
+      </c>
+      <c r="F131" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B132" t="inlineStr">
+        <is>
+          <t>elderly physical activity</t>
+        </is>
+      </c>
+      <c r="C132" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D132" t="n">
+        <v>85</v>
+      </c>
+      <c r="E132" t="n">
+        <v>54</v>
+      </c>
+      <c r="F132" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/exercise-for-elderly-staying-active-at-any-age</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B133" t="inlineStr">
+        <is>
+          <t>grandma robot</t>
+        </is>
+      </c>
+      <c r="C133" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D133" t="n">
+        <v>55</v>
+      </c>
+      <c r="E133" t="n">
+        <v>14</v>
+      </c>
+      <c r="F133" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B134" t="inlineStr">
+        <is>
+          <t>personal ai companion</t>
+        </is>
+      </c>
+      <c r="C134" t="n">
+        <v>1600</v>
+      </c>
+      <c r="D134" t="n">
+        <v>53</v>
+      </c>
+      <c r="E134" t="n">
+        <v>65</v>
+      </c>
+      <c r="F134" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B135" t="inlineStr">
+        <is>
+          <t>elderly people stereotypes</t>
+        </is>
+      </c>
+      <c r="C135" t="n">
+        <v>720</v>
+      </c>
+      <c r="D135" t="n">
+        <v>7</v>
+      </c>
+      <c r="E135" t="n">
+        <v>3</v>
+      </c>
+      <c r="F135" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>eliq</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>720</v>
+      </c>
+      <c r="D136" t="n">
+        <v>2</v>
+      </c>
+      <c r="E136" t="n">
+        <v>9</v>
+      </c>
+      <c r="F136" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>old age stereotypes</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>720</v>
+      </c>
+      <c r="D137" t="n">
+        <v>12</v>
+      </c>
+      <c r="E137" t="n">
+        <v>8</v>
+      </c>
+      <c r="F137" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>old people stereotypes</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>720</v>
+      </c>
+      <c r="D138" t="n">
+        <v>6</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0</v>
+      </c>
+      <c r="F138" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>physical activity for older adults</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>720</v>
+      </c>
+      <c r="D139" t="n">
+        <v>107</v>
+      </c>
+      <c r="E139" t="n">
+        <v>57</v>
+      </c>
+      <c r="F139" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/exercise-for-elderly-staying-active-at-any-age</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>robot companions for adults</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>720</v>
+      </c>
+      <c r="D140" t="n">
+        <v>5</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0</v>
+      </c>
+      <c r="F140" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B141" t="inlineStr">
+        <is>
+          <t>stereotypes about older people</t>
+        </is>
+      </c>
+      <c r="C141" t="n">
+        <v>720</v>
+      </c>
+      <c r="D141" t="n">
+        <v>15</v>
+      </c>
+      <c r="E141" t="n">
+        <v>9</v>
+      </c>
+      <c r="F141" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B142" t="inlineStr">
+        <is>
+          <t>stereotypes elderly</t>
+        </is>
+      </c>
+      <c r="C142" t="n">
+        <v>720</v>
+      </c>
+      <c r="D142" t="n">
+        <v>7</v>
+      </c>
+      <c r="E142" t="n">
+        <v>3</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B143" t="inlineStr">
+        <is>
+          <t>stereotypes of elderly</t>
+        </is>
+      </c>
+      <c r="C143" t="n">
+        <v>720</v>
+      </c>
+      <c r="D143" t="n">
+        <v>6</v>
+      </c>
+      <c r="E143" t="n">
+        <v>12</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B144" t="inlineStr">
+        <is>
+          <t>stereotypes of the elderly</t>
+        </is>
+      </c>
+      <c r="C144" t="n">
+        <v>720</v>
+      </c>
+      <c r="D144" t="n">
+        <v>9</v>
+      </c>
+      <c r="E144" t="n">
+        <v>0</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B145" t="inlineStr">
+        <is>
+          <t>elder app</t>
+        </is>
+      </c>
+      <c r="C145" t="n">
+        <v>590</v>
+      </c>
+      <c r="D145" t="n">
+        <v>37</v>
+      </c>
+      <c r="E145" t="n">
+        <v>11</v>
+      </c>
+      <c r="F145" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B146" t="inlineStr">
+        <is>
+          <t>elli q</t>
+        </is>
+      </c>
+      <c r="C146" t="n">
+        <v>590</v>
+      </c>
+      <c r="D146" t="n">
+        <v>1</v>
+      </c>
+      <c r="E146" t="n">
+        <v>14</v>
+      </c>
+      <c r="F146" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B147" t="inlineStr">
+        <is>
+          <t>ageist examples</t>
+        </is>
+      </c>
+      <c r="C147" t="n">
+        <v>480</v>
+      </c>
+      <c r="D147" t="n">
+        <v>14</v>
+      </c>
+      <c r="E147" t="n">
+        <v>16</v>
+      </c>
+      <c r="F147" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/5-inspiring-seniors-defying-age-stereotypes</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B148" t="inlineStr">
+        <is>
+          <t>elliq robot</t>
+        </is>
+      </c>
+      <c r="C148" t="n">
+        <v>480</v>
+      </c>
+      <c r="D148" t="n">
+        <v>2</v>
+      </c>
+      <c r="E148" t="n">
+        <v>27</v>
+      </c>
+      <c r="F148" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B149" t="inlineStr">
+        <is>
+          <t>intuition robotics</t>
+        </is>
+      </c>
+      <c r="C149" t="n">
+        <v>480</v>
+      </c>
+      <c r="D149" t="n">
+        <v>2</v>
+      </c>
+      <c r="E149" t="n">
+        <v>12</v>
+      </c>
+      <c r="F149" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B150" t="inlineStr">
+        <is>
+          <t>older adults and exercise</t>
+        </is>
+      </c>
+      <c r="C150" t="n">
+        <v>480</v>
+      </c>
+      <c r="D150" t="n">
+        <v>82</v>
+      </c>
+      <c r="E150" t="n">
+        <v>39</v>
+      </c>
+      <c r="F150" t="inlineStr">
+        <is>
+          <t>https://blog.elliq.com/exercise-for-elderly-staying-active-at-any-age</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>ElliQ</t>
+        </is>
+      </c>
+      <c r="B151" t="inlineStr">
+        <is>
+          <t>smart home companion robot</t>
+        </is>
+      </c>
+      <c r="C151" t="n">
+        <v>480</v>
+      </c>
+      <c r="D151" t="n">
+        <v>11</v>
+      </c>
+      <c r="E151" t="n">
+        <v>19</v>
+      </c>
+      <c r="F151" t="inlineStr">
+        <is>
+          <t>https://elliq.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>elderly care</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>201000</v>
+      </c>
+      <c r="D152" t="n">
+        <v>20</v>
+      </c>
+      <c r="E152" t="n">
+        <v>76</v>
+      </c>
+      <c r="F152" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>elderly caring</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>201000</v>
+      </c>
+      <c r="D153" t="n">
+        <v>30</v>
+      </c>
+      <c r="E153" t="n">
+        <v>63</v>
+      </c>
+      <c r="F153" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>papa</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D154" t="n">
+        <v>1</v>
+      </c>
+      <c r="E154" t="n">
+        <v>48</v>
+      </c>
+      <c r="F154" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>papas</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>165000</v>
+      </c>
+      <c r="D155" t="n">
+        <v>43</v>
+      </c>
+      <c r="E155" t="n">
+        <v>33</v>
+      </c>
+      <c r="F155" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>care and companion</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>90500</v>
+      </c>
+      <c r="D156" t="n">
+        <v>5</v>
+      </c>
+      <c r="E156" t="n">
+        <v>2</v>
+      </c>
+      <c r="F156" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>care companionship</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>90500</v>
+      </c>
+      <c r="D157" t="n">
+        <v>2</v>
+      </c>
+      <c r="E157" t="n">
+        <v>14</v>
+      </c>
+      <c r="F157" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>companion care</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>90500</v>
+      </c>
+      <c r="D158" t="n">
+        <v>12</v>
+      </c>
+      <c r="E158" t="n">
+        <v>18</v>
+      </c>
+      <c r="F158" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B159" t="inlineStr">
+        <is>
+          <t>companions care</t>
+        </is>
+      </c>
+      <c r="C159" t="n">
+        <v>90500</v>
+      </c>
+      <c r="D159" t="n">
+        <v>3</v>
+      </c>
+      <c r="E159" t="n">
+        <v>19</v>
+      </c>
+      <c r="F159" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B160" t="inlineStr">
+        <is>
+          <t>companionship care</t>
+        </is>
+      </c>
+      <c r="C160" t="n">
+        <v>90500</v>
+      </c>
+      <c r="D160" t="n">
+        <v>6</v>
+      </c>
+      <c r="E160" t="n">
+        <v>29</v>
+      </c>
+      <c r="F160" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B161" t="inlineStr">
+        <is>
+          <t>companionship carer</t>
+        </is>
+      </c>
+      <c r="C161" t="n">
+        <v>90500</v>
+      </c>
+      <c r="D161" t="n">
+        <v>2</v>
+      </c>
+      <c r="E161" t="n">
+        <v>9</v>
+      </c>
+      <c r="F161" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B162" t="inlineStr">
+        <is>
+          <t>elder homecare</t>
+        </is>
+      </c>
+      <c r="C162" t="n">
+        <v>90500</v>
+      </c>
+      <c r="D162" t="n">
+        <v>67</v>
+      </c>
+      <c r="E162" t="n">
+        <v>30</v>
+      </c>
+      <c r="F162" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B163" t="inlineStr">
+        <is>
+          <t>pappa bar</t>
+        </is>
+      </c>
+      <c r="C163" t="n">
+        <v>74000</v>
+      </c>
+      <c r="D163" t="n">
+        <v>62</v>
+      </c>
+      <c r="E163" t="n">
+        <v>12</v>
+      </c>
+      <c r="F163" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B164" t="inlineStr">
+        <is>
+          <t>elderly care in-home services</t>
+        </is>
+      </c>
+      <c r="C164" t="n">
+        <v>60500</v>
+      </c>
+      <c r="D164" t="n">
+        <v>54</v>
+      </c>
+      <c r="E164" t="n">
+        <v>82</v>
+      </c>
+      <c r="F164" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B165" t="inlineStr">
+        <is>
+          <t>home care services for seniors</t>
+        </is>
+      </c>
+      <c r="C165" t="n">
+        <v>60500</v>
+      </c>
+      <c r="D165" t="n">
+        <v>26</v>
+      </c>
+      <c r="E165" t="n">
+        <v>81</v>
+      </c>
+      <c r="F165" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B166" t="inlineStr">
+        <is>
+          <t>trusted home sitter</t>
+        </is>
+      </c>
+      <c r="C166" t="n">
+        <v>60500</v>
+      </c>
+      <c r="D166" t="n">
+        <v>62</v>
+      </c>
+      <c r="E166" t="n">
+        <v>31</v>
+      </c>
+      <c r="F166" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B167" t="inlineStr">
+        <is>
+          <t>health uber</t>
+        </is>
+      </c>
+      <c r="C167" t="n">
+        <v>40500</v>
+      </c>
+      <c r="D167" t="n">
+        <v>60</v>
+      </c>
+      <c r="E167" t="n">
+        <v>21</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B168" t="inlineStr">
+        <is>
+          <t>home caregivers for seniors</t>
+        </is>
+      </c>
+      <c r="C168" t="n">
+        <v>40500</v>
+      </c>
+      <c r="D168" t="n">
+        <v>57</v>
+      </c>
+      <c r="E168" t="n">
+        <v>78</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B169" t="inlineStr">
+        <is>
+          <t>in home eldercare</t>
+        </is>
+      </c>
+      <c r="C169" t="n">
+        <v>40500</v>
+      </c>
+      <c r="D169" t="n">
+        <v>32</v>
+      </c>
+      <c r="E169" t="n">
+        <v>80</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B170" t="inlineStr">
+        <is>
+          <t>in-home support services</t>
+        </is>
+      </c>
+      <c r="C170" t="n">
+        <v>40500</v>
+      </c>
+      <c r="D170" t="n">
+        <v>42</v>
+      </c>
+      <c r="E170" t="n">
+        <v>34</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B171" t="inlineStr">
+        <is>
+          <t>personal care assistant</t>
+        </is>
+      </c>
+      <c r="C171" t="n">
+        <v>40500</v>
+      </c>
+      <c r="D171" t="n">
+        <v>1</v>
+      </c>
+      <c r="E171" t="n">
+        <v>3</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/resources/blog/whats-the-difference-between-personal-care-aide-and-caregiver</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B172" t="inlineStr">
+        <is>
+          <t>elderly in home assistance</t>
+        </is>
+      </c>
+      <c r="C172" t="n">
+        <v>33100</v>
+      </c>
+      <c r="D172" t="n">
+        <v>28</v>
+      </c>
+      <c r="E172" t="n">
+        <v>76</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B173" t="inlineStr">
+        <is>
+          <t>friends apps for adults</t>
+        </is>
+      </c>
+      <c r="C173" t="n">
+        <v>33100</v>
+      </c>
+      <c r="D173" t="n">
+        <v>86</v>
+      </c>
+      <c r="E173" t="n">
+        <v>20</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B174" t="inlineStr">
+        <is>
+          <t>poppa house</t>
+        </is>
+      </c>
+      <c r="C174" t="n">
+        <v>33100</v>
+      </c>
+      <c r="D174" t="n">
+        <v>87</v>
+      </c>
+      <c r="E174" t="n">
+        <v>17</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B175" t="inlineStr">
+        <is>
+          <t>application for money</t>
+        </is>
+      </c>
+      <c r="C175" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D175" t="n">
+        <v>32</v>
+      </c>
+      <c r="E175" t="n">
+        <v>59</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/pals</t>
+        </is>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B176" t="inlineStr">
+        <is>
+          <t>internet pals</t>
+        </is>
+      </c>
+      <c r="C176" t="n">
+        <v>27100</v>
+      </c>
+      <c r="D176" t="n">
+        <v>22</v>
+      </c>
+      <c r="E176" t="n">
+        <v>47</v>
+      </c>
+      <c r="F176" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B177" t="inlineStr">
+        <is>
+          <t>at home moms jobs</t>
+        </is>
+      </c>
+      <c r="C177" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D177" t="n">
+        <v>8</v>
+      </c>
+      <c r="E177" t="n">
+        <v>6</v>
+      </c>
+      <c r="F177" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/resources/blog/4-best-part-time-jobs-for-stay-at-home-moms</t>
+        </is>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B178" t="inlineStr">
+        <is>
+          <t>companion homecare</t>
+        </is>
+      </c>
+      <c r="C178" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D178" t="n">
+        <v>19</v>
+      </c>
+      <c r="E178" t="n">
+        <v>0</v>
+      </c>
+      <c r="F178" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B179" t="inlineStr">
+        <is>
+          <t>define companionship</t>
+        </is>
+      </c>
+      <c r="C179" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D179" t="n">
+        <v>38</v>
+      </c>
+      <c r="E179" t="n">
+        <v>14</v>
+      </c>
+      <c r="F179" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B180" t="inlineStr">
+        <is>
+          <t>errands meaning</t>
+        </is>
+      </c>
+      <c r="C180" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D180" t="n">
+        <v>46</v>
+      </c>
+      <c r="E180" t="n">
+        <v>1</v>
+      </c>
+      <c r="F180" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>Papa</t>
+        </is>
+      </c>
+      <c r="B181" t="inlineStr">
+        <is>
+          <t>home care companions</t>
+        </is>
+      </c>
+      <c r="C181" t="n">
+        <v>22200</v>
+      </c>
+      <c r="D181" t="n">
+        <v>10</v>
+      </c>
+      <c r="E181" t="n">
+        <v>18</v>
+      </c>
+      <c r="F181" t="inlineStr">
+        <is>
+          <t>https://www.papa.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B182" t="inlineStr">
+        <is>
+          <t>friend</t>
+        </is>
+      </c>
+      <c r="C182" t="n">
+        <v>823000</v>
+      </c>
+      <c r="D182" t="n">
+        <v>3</v>
+      </c>
+      <c r="E182" t="n">
+        <v>37</v>
+      </c>
+      <c r="F182" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B183" t="inlineStr">
+        <is>
+          <t>frienps</t>
+        </is>
+      </c>
+      <c r="C183" t="n">
+        <v>823000</v>
+      </c>
+      <c r="D183" t="n">
+        <v>56</v>
+      </c>
+      <c r="E183" t="n">
+        <v>65</v>
+      </c>
+      <c r="F183" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B184" t="inlineStr">
+        <is>
+          <t>the friendships</t>
+        </is>
+      </c>
+      <c r="C184" t="n">
+        <v>49500</v>
+      </c>
+      <c r="D184" t="n">
+        <v>65</v>
+      </c>
+      <c r="E184" t="n">
+        <v>21</v>
+      </c>
+      <c r="F184" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B185" t="inlineStr">
+        <is>
+          <t>design with friend</t>
+        </is>
+      </c>
+      <c r="C185" t="n">
+        <v>14800</v>
+      </c>
+      <c r="D185" t="n">
+        <v>36</v>
+      </c>
+      <c r="E185" t="n">
+        <v>4</v>
+      </c>
+      <c r="F185" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B186" t="inlineStr">
+        <is>
+          <t>a i friend</t>
+        </is>
+      </c>
+      <c r="C186" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D186" t="n">
+        <v>2</v>
+      </c>
+      <c r="E186" t="n">
+        <v>62</v>
+      </c>
+      <c r="F186" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B187" t="inlineStr">
+        <is>
+          <t>a i friends</t>
+        </is>
+      </c>
+      <c r="C187" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D187" t="n">
+        <v>9</v>
+      </c>
+      <c r="E187" t="n">
+        <v>24</v>
+      </c>
+      <c r="F187" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B188" t="inlineStr">
+        <is>
+          <t>ai friend</t>
+        </is>
+      </c>
+      <c r="C188" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D188" t="n">
+        <v>5</v>
+      </c>
+      <c r="E188" t="n">
+        <v>35</v>
+      </c>
+      <c r="F188" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B189" t="inlineStr">
+        <is>
+          <t>ai friendship</t>
+        </is>
+      </c>
+      <c r="C189" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D189" t="n">
+        <v>5</v>
+      </c>
+      <c r="E189" t="n">
+        <v>33</v>
+      </c>
+      <c r="F189" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B190" t="inlineStr">
+        <is>
+          <t>application for friendship</t>
+        </is>
+      </c>
+      <c r="C190" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D190" t="n">
+        <v>22</v>
+      </c>
+      <c r="E190" t="n">
+        <v>20</v>
+      </c>
+      <c r="F190" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B191" t="inlineStr">
+        <is>
+          <t>friend ai</t>
+        </is>
+      </c>
+      <c r="C191" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D191" t="n">
+        <v>1</v>
+      </c>
+      <c r="E191" t="n">
+        <v>46</v>
+      </c>
+      <c r="F191" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B192" t="inlineStr">
+        <is>
+          <t>friend ia</t>
+        </is>
+      </c>
+      <c r="C192" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D192" t="n">
+        <v>1</v>
+      </c>
+      <c r="E192" t="n">
+        <v>14</v>
+      </c>
+      <c r="F192" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B193" t="inlineStr">
+        <is>
+          <t>friends application</t>
+        </is>
+      </c>
+      <c r="C193" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D193" t="n">
+        <v>4</v>
+      </c>
+      <c r="E193" t="n">
+        <v>44</v>
+      </c>
+      <c r="F193" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B194" t="inlineStr">
+        <is>
+          <t>friendship ai</t>
+        </is>
+      </c>
+      <c r="C194" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D194" t="n">
+        <v>5</v>
+      </c>
+      <c r="E194" t="n">
+        <v>34</v>
+      </c>
+      <c r="F194" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B195" t="inlineStr">
+        <is>
+          <t>friendships ai</t>
+        </is>
+      </c>
+      <c r="C195" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D195" t="n">
+        <v>18</v>
+      </c>
+      <c r="E195" t="n">
+        <v>9</v>
+      </c>
+      <c r="F195" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B196" t="inlineStr">
+        <is>
+          <t>locket apps</t>
+        </is>
+      </c>
+      <c r="C196" t="n">
+        <v>12100</v>
+      </c>
+      <c r="D196" t="n">
+        <v>45</v>
+      </c>
+      <c r="E196" t="n">
+        <v>8</v>
+      </c>
+      <c r="F196" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B197" t="inlineStr">
+        <is>
+          <t>frend</t>
+        </is>
+      </c>
+      <c r="C197" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D197" t="n">
+        <v>20</v>
+      </c>
+      <c r="E197" t="n">
+        <v>4</v>
+      </c>
+      <c r="F197" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B198" t="inlineStr">
+        <is>
+          <t>frends</t>
+        </is>
+      </c>
+      <c r="C198" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D198" t="n">
+        <v>41</v>
+      </c>
+      <c r="E198" t="n">
+        <v>19</v>
+      </c>
+      <c r="F198" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B199" t="inlineStr">
+        <is>
+          <t>friends internet</t>
+        </is>
+      </c>
+      <c r="C199" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D199" t="n">
+        <v>20</v>
+      </c>
+      <c r="E199" t="n">
+        <v>15</v>
+      </c>
+      <c r="F199" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B200" t="inlineStr">
+        <is>
+          <t>friendship code</t>
+        </is>
+      </c>
+      <c r="C200" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D200" t="n">
+        <v>77</v>
+      </c>
+      <c r="E200" t="n">
+        <v>0</v>
+      </c>
+      <c r="F200" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B201" t="inlineStr">
+        <is>
+          <t>gadget startup</t>
+        </is>
+      </c>
+      <c r="C201" t="n">
+        <v>8100</v>
+      </c>
+      <c r="D201" t="n">
+        <v>19</v>
+      </c>
+      <c r="E201" t="n">
+        <v>0</v>
+      </c>
+      <c r="F201" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="202">
+      <c r="A202" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B202" t="inlineStr">
+        <is>
+          <t>best friendship necklace</t>
+        </is>
+      </c>
+      <c r="C202" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D202" t="n">
+        <v>44</v>
+      </c>
+      <c r="E202" t="n">
+        <v>0</v>
+      </c>
+      <c r="F202" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="203">
+      <c r="A203" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B203" t="inlineStr">
+        <is>
+          <t>best friendship necklaces</t>
+        </is>
+      </c>
+      <c r="C203" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D203" t="n">
+        <v>80</v>
+      </c>
+      <c r="E203" t="n">
+        <v>0</v>
+      </c>
+      <c r="F203" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="204">
+      <c r="A204" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B204" t="inlineStr">
+        <is>
+          <t>friends finders</t>
+        </is>
+      </c>
+      <c r="C204" t="n">
+        <v>6600</v>
+      </c>
+      <c r="D204" t="n">
+        <v>15</v>
+      </c>
+      <c r="E204" t="n">
+        <v>28</v>
+      </c>
+      <c r="F204" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="205">
+      <c r="A205" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B205" t="inlineStr">
+        <is>
+          <t>freund</t>
+        </is>
+      </c>
+      <c r="C205" t="n">
+        <v>5400</v>
+      </c>
+      <c r="D205" t="n">
+        <v>44</v>
+      </c>
+      <c r="E205" t="n">
+        <v>25</v>
+      </c>
+      <c r="F205" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="206">
+      <c r="A206" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B206" t="inlineStr">
+        <is>
+          <t>find and friend</t>
+        </is>
+      </c>
+      <c r="C206" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D206" t="n">
+        <v>34</v>
+      </c>
+      <c r="E206" t="n">
+        <v>45</v>
+      </c>
+      <c r="F206" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="207">
+      <c r="A207" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B207" t="inlineStr">
+        <is>
+          <t>friend com</t>
+        </is>
+      </c>
+      <c r="C207" t="n">
+        <v>4400</v>
+      </c>
+      <c r="D207" t="n">
+        <v>1</v>
+      </c>
+      <c r="E207" t="n">
+        <v>33</v>
+      </c>
+      <c r="F207" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="208">
+      <c r="A208" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B208" t="inlineStr">
+        <is>
+          <t>new fiend</t>
+        </is>
+      </c>
+      <c r="C208" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D208" t="n">
+        <v>75</v>
+      </c>
+      <c r="E208" t="n">
+        <v>0</v>
+      </c>
+      <c r="F208" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="209">
+      <c r="A209" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B209" t="inlineStr">
+        <is>
+          <t>new friend</t>
+        </is>
+      </c>
+      <c r="C209" t="n">
+        <v>3600</v>
+      </c>
+      <c r="D209" t="n">
+        <v>30</v>
+      </c>
+      <c r="E209" t="n">
+        <v>14</v>
+      </c>
+      <c r="F209" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="210">
+      <c r="A210" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B210" t="inlineStr">
+        <is>
+          <t>a friend</t>
+        </is>
+      </c>
+      <c r="C210" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D210" t="n">
+        <v>33</v>
+      </c>
+      <c r="E210" t="n">
+        <v>12</v>
+      </c>
+      <c r="F210" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
+        </is>
+      </c>
+    </row>
+    <row r="211">
+      <c r="A211" t="inlineStr">
+        <is>
+          <t>friend.com</t>
+        </is>
+      </c>
+      <c r="B211" t="inlineStr">
+        <is>
+          <t>a friends</t>
+        </is>
+      </c>
+      <c r="C211" t="n">
+        <v>2900</v>
+      </c>
+      <c r="D211" t="n">
+        <v>20</v>
+      </c>
+      <c r="E211" t="n">
+        <v>15</v>
+      </c>
+      <c r="F211" t="inlineStr">
+        <is>
+          <t>https://friend.com/</t>
         </is>
       </c>
     </row>
@@ -4747,7 +7087,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Generated: 2026-05-12 11:56 UTC</t>
+          <t>Generated: 2026-05-15 18:11 UTC</t>
         </is>
       </c>
     </row>
@@ -4766,7 +7106,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0</v>
+        <v>100</v>
       </c>
     </row>
     <row r="6">
@@ -4776,7 +7116,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0</v>
+        <v>10</v>
       </c>
     </row>
   </sheetData>
